--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/bio-bio.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/bio-bio.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9946.959999999999</v>
+        <v>9892.59</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>19664.36</v>
+        <v>19556.67</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24335.22</v>
+        <v>24201.95</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10569.83</v>
+        <v>10752.28</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12244.52</v>
+        <v>12194.06</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13775.39</v>
+        <v>13846.53</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13143.96</v>
+        <v>13194.41</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12734.25</v>
+        <v>12821.9</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6323.08</v>
+        <v>6366.61</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>9943.059999999999</v>
+        <v>10011.5</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9430.299999999999</v>
+        <v>9510.889999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7673.64</v>
+        <v>7755.95</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11843.25</v>
+        <v>12131.25</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13734.61</v>
+        <v>14341.16</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>12849.78</v>
+        <v>12814.34</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>16310.24</v>
+        <v>16269.06</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>18887.13</v>
+        <v>19027.83</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11700.33</v>
+        <v>11649.04</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>12544.31</v>
+        <v>12513.33</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>12338.38</v>
+        <v>12377.65</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>10194.49</v>
+        <v>10117.15</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>22348.76</v>
+        <v>22179.22</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14722.92</v>
+        <v>14611.23</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8386.389999999999</v>
+        <v>8444.290000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10063.67</v>
+        <v>9929.620000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>22291.54</v>
+        <v>21833.41</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>11789.85</v>
+        <v>11835.75</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>17420.96</v>
+        <v>17534.53</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10324.67</v>
+        <v>10348.34</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>21993.99</v>
+        <v>22141.2</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>11005.71</v>
+        <v>11082.73</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/bio-bio.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4858-1013-CM25</t>
+          <t>2704-1496-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9892.59</v>
+        <v>14609.82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>654-400-CM25</t>
+          <t>2360-668-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>19556.67</v>
+        <v>9014.040000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>654-403-CM25</t>
+          <t>4858-1013-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,22 +651,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24201.95</v>
+        <v>9892.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2409-1784-CM25</t>
+          <t>654-400-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10752.28</v>
+        <v>19556.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1208129-730-CM25</t>
+          <t>654-403-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12194.06</v>
+        <v>24201.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4238-396-CM25</t>
+          <t>2409-1784-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13846.53</v>
+        <v>10752.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2178-421-CM25</t>
+          <t>1208129-730-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13194.41</v>
+        <v>12194.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2410-2654-CM25</t>
+          <t>4238-396-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12821.9</v>
+        <v>13846.53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2410-2655-CM25</t>
+          <t>2178-421-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6366.61</v>
+        <v>13194.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2410-2656-CM25</t>
+          <t>2410-2654-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10011.5</v>
+        <v>12821.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1563-93-CM25</t>
+          <t>2410-2655-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9510.889999999999</v>
+        <v>6366.61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2178-432-CM25</t>
+          <t>2410-2656-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7755.95</v>
+        <v>10011.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4375-188-CM26</t>
+          <t>1563-93-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>suria ltda</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.827.520-1</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12131.25</v>
+        <v>9510.889999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1079576-107-CM26</t>
+          <t>2178-432-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>14341.16</v>
+        <v>7755.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1456840-15-CM26</t>
+          <t>4375-188-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.981.460-6</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.827.520-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>12814.34</v>
+        <v>12131.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4034-206-CM26</t>
+          <t>1079576-107-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>SECCIÓN COMPRAS VIII ZONA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>16269.06</v>
+        <v>14341.16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1426098-122-CM26</t>
+          <t>1456840-15-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.981.460-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>19027.83</v>
+        <v>12814.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4494-279-CM26</t>
+          <t>4034-206-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>Ilustre Municipalidad de Cañete - Educación</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11649.04</v>
+        <v>16269.06</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2421-599-CM26</t>
+          <t>1426098-122-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>12513.33</v>
+        <v>19027.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1079650-29-SE26</t>
+          <t>4494-279-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,32 +1713,28 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>BLUEMEDICAL SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.116.604-2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>12377.65</v>
+        <v>11649.04</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1057432-197-CM26</t>
+          <t>2421-599-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>Dirección de Administración de Salud Municipal</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>10117.15</v>
+        <v>12513.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057934-10-CM26</t>
+          <t>1079650-29-SE26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,28 +1835,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>BLUEMEDICAL SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>76.116.604-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>22179.22</v>
+        <v>12377.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4081-202-CM26</t>
+          <t>1057432-197-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14611.23</v>
+        <v>10117.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2760-71-CM26</t>
+          <t>1057934-10-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1936,22 +1936,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>61.607.202-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8444.290000000001</v>
+        <v>22179.22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1079650-57-CM26</t>
+          <t>4081-202-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>Ilustre Municipalidad de Cabrero</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>92.999.000-5</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9929.620000000001</v>
+        <v>14611.23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2178-186-CM26</t>
+          <t>2760-71-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,22 +2058,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.151.200-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>21833.41</v>
+        <v>8444.290000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>654-246-CM26</t>
+          <t>1079650-57-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>IMPORTADORA Y DISTRIBUIDORA ARQUIMED LTDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>92.999.000-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>11835.75</v>
+        <v>9929.620000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057822-13-CM26</t>
+          <t>2178-186-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,27 +2175,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.607.100-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>17534.53</v>
+        <v>21833.41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2704-1424-CM26</t>
+          <t>654-246-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.911.006-6</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DEL BIO BIO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10348.34</v>
+        <v>11835.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>654-256-CM26</t>
+          <t>1057822-13-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>22141.2</v>
+        <v>17534.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1777-67-CM26</t>
+          <t>2704-1424-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.804.012-9</t>
+          <t>60.911.006-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+          <t>UNIVERSIDAD DEL BIO BIO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.028.554-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2403,6 +2403,128 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
+        <v>10348.34</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>654-256-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>61.820.004-3</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>22141.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1777-67-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.804.012-9</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>11082.73</v>
       </c>
     </row>
